--- a/outputs/97-36.xlsx
+++ b/outputs/97-36.xlsx
@@ -20,15 +20,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
-  <si>
-    <t xml:space="preserve">https://www.ladbrokes.com.au/horse-racing/domestic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.ladbrokes.com.au/racing/ballarat/ebaa02b4-e4ba-4427-aa83-db688c34c466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.ladbrokes.com.au/racing/ballarat/a6009afb-4ac2-41d6-b098-fca06b9d03cf</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t xml:space="preserve">' Delete all rows above the row containing "domestic"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub DeleteRowsAbove()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dim ws As Worksheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dim rng As Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dim found As Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dim lastRow As Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dim foundRow As Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' Reference the active sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Set ws = ActiveSheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' Find the last used row in column A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    lastRow = ws.Cells(ws.Rows.Count, 1).End(xlUp).Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' Search for "domestic" starting from the first row and first column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Set found = ws.Range("A1:A" &amp; lastRow).Find(What:="domestic", LookIn:=xlValues)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' If found, delete all rows above it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    If Not found Is Nothing Then</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ws.Rows("1:" &amp; found.Row - 1).Delete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    End If</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Sub</t>
   </si>
 </sst>
 </file>
@@ -104,8 +149,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -298,27 +347,97 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>1</v>
+      <c r="A3" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>2</v>
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/97-36.xlsx
+++ b/outputs/97-36.xlsx
@@ -20,60 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
-    <t xml:space="preserve">' Delete all rows above the row containing "domestic"</t>
+    <t xml:space="preserve">https://www.ladbrokes.com.au/horse-racing/domestic</t>
   </si>
   <si>
-    <t xml:space="preserve">Sub DeleteRowsAbove()</t>
+    <t xml:space="preserve">https://www.ladbrokes.com.au/racing/ballarat/ebaa02b4-e4ba-4427-aa83-db688c34c466</t>
   </si>
   <si>
-    <t xml:space="preserve">    Dim ws As Worksheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Dim rng As Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Dim found As Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Dim lastRow As Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Dim foundRow As Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ' Reference the active sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Set ws = ActiveSheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ' Find the last used row in column A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    lastRow = ws.Cells(ws.Rows.Count, 1).End(xlUp).Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ' Search for "domestic" starting from the first row and first column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Set found = ws.Range("A1:A" &amp; lastRow).Find(What:="domestic", LookIn:=xlValues)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ' If found, delete all rows above it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    If Not found Is Nothing Then</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ws.Rows("1:" &amp; found.Row - 1).Delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    End If</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End Sub</t>
+    <t xml:space="preserve">https://www.ladbrokes.com.au/racing/ballarat/a6009afb-4ac2-41d6-b098-fca06b9d03cf</t>
   </si>
 </sst>
 </file>
@@ -347,7 +302,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -362,82 +317,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
